--- a/GameTable/Config/ArchiveConfig.xlsx
+++ b/GameTable/Config/ArchiveConfig.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D7"/>
+  <dimension ref="A1:C7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -429,11 +429,6 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Type</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
           <t>Description</t>
         </is>
       </c>
@@ -454,11 +449,6 @@
           <t>string</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -471,11 +461,6 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>float</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
           <t>最大生命值</t>
         </is>
       </c>
@@ -491,11 +476,6 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>float</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
           <t>最大魔法值</t>
         </is>
       </c>
@@ -511,11 +491,6 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
           <t>攻击力</t>
         </is>
       </c>
@@ -531,11 +506,6 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
           <t>防御力</t>
         </is>
       </c>
@@ -548,11 +518,6 @@
       </c>
       <c r="B7" t="n">
         <v>12</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
       </c>
     </row>
   </sheetData>
